--- a/tasks/finalpool/sf-canvas-training-impact-excel-ppt/groundtruth_workspace/Training_Impact_Analysis.xlsx
+++ b/tasks/finalpool/sf-canvas-training-impact-excel-ppt/groundtruth_workspace/Training_Impact_Analysis.xlsx
@@ -455,13 +455,13 @@
         <v>7096</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="D2" t="n">
         <v>58991.61</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -474,13 +474,13 @@
         <v>7148</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="D3" t="n">
         <v>57878.19</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         <v>7077</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
         <v>58920.45</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5">
@@ -512,13 +512,13 @@
         <v>7120</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="D5" t="n">
         <v>57808.74</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>7083</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
         <v>57905.93</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -550,13 +550,13 @@
         <v>7232</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="D7" t="n">
         <v>58864.79</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8">
@@ -569,13 +569,13 @@
         <v>7244</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="n">
         <v>58400.48</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500</v>
+        <v>383</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>400</v>
+        <v>2237</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>350</v>
+        <v>2498</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="5">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>450</v>
+        <v>1938</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Applied Analytics &amp; Algorithms (Fall 2013)</t>
+          <t>Creative Computing &amp; Culture (Fall 2014)</t>
         </is>
       </c>
     </row>
